--- a/Fig.S9(b).xlsx
+++ b/Fig.S9(b).xlsx
@@ -380,7 +380,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -391,7 +391,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -402,7 +402,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -413,7 +413,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -424,7 +424,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -435,7 +435,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -443,10 +443,10 @@
         <v>5</v>
       </c>
       <c r="B12">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C12">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -454,10 +454,10 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C13">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -465,10 +465,10 @@
         <v>7</v>
       </c>
       <c r="B14">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C14">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -476,10 +476,10 @@
         <v>8</v>
       </c>
       <c r="B15">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C15">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -487,10 +487,10 @@
         <v>9</v>
       </c>
       <c r="B16">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C16">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -498,10 +498,10 @@
         <v>10</v>
       </c>
       <c r="B17">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C17">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -534,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -567,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -575,10 +575,10 @@
         <v>15</v>
       </c>
       <c r="B24">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C24">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +586,10 @@
         <v>16</v>
       </c>
       <c r="B25">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C25">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -597,10 +597,10 @@
         <v>17</v>
       </c>
       <c r="B26">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C26">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -608,10 +608,10 @@
         <v>18</v>
       </c>
       <c r="B27">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C27">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -619,10 +619,10 @@
         <v>19</v>
       </c>
       <c r="B28">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C28">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +630,10 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C29">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,10 +707,10 @@
         <v>25</v>
       </c>
       <c r="B36">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C36">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,10 +718,10 @@
         <v>26</v>
       </c>
       <c r="B37">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C37">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,10 +729,10 @@
         <v>27</v>
       </c>
       <c r="B38">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C38">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,10 +740,10 @@
         <v>28</v>
       </c>
       <c r="B39">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C39">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>29</v>
       </c>
       <c r="B40">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C40">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,10 +762,10 @@
         <v>30</v>
       </c>
       <c r="B41">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C41">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="C47">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>35</v>
       </c>
       <c r="B48">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C48">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>36</v>
       </c>
       <c r="B49">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C49">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +861,10 @@
         <v>37</v>
       </c>
       <c r="B50">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C50">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -872,10 +872,10 @@
         <v>38</v>
       </c>
       <c r="B51">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C51">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -883,10 +883,10 @@
         <v>39</v>
       </c>
       <c r="B52">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C52">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -894,10 +894,10 @@
         <v>40</v>
       </c>
       <c r="B53">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C53">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="C54">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="C55">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -930,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="C56">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="C57">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="C58">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="C59">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -971,10 +971,10 @@
         <v>45</v>
       </c>
       <c r="B60">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C60">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,10 +982,10 @@
         <v>46</v>
       </c>
       <c r="B61">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C61">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -993,10 +993,10 @@
         <v>47</v>
       </c>
       <c r="B62">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C62">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1004,10 +1004,10 @@
         <v>48</v>
       </c>
       <c r="B63">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C63">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1015,10 +1015,10 @@
         <v>49</v>
       </c>
       <c r="B64">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C64">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>50</v>
       </c>
       <c r="B65">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C65">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="C66">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="C67">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="C68">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="C69">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="C70">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="C71">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1103,10 +1103,10 @@
         <v>55</v>
       </c>
       <c r="B72">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C72">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1114,10 +1114,10 @@
         <v>56</v>
       </c>
       <c r="B73">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C73">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1125,10 +1125,10 @@
         <v>57</v>
       </c>
       <c r="B74">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C74">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1136,10 +1136,10 @@
         <v>58</v>
       </c>
       <c r="B75">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C75">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1147,10 +1147,10 @@
         <v>59</v>
       </c>
       <c r="B76">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C76">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1158,10 +1158,10 @@
         <v>60</v>
       </c>
       <c r="B77">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C77">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1172,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="C78">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="C79">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="C80">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="C81">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="C82">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="C83">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1235,10 +1235,10 @@
         <v>65</v>
       </c>
       <c r="B84">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C84">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1246,10 +1246,10 @@
         <v>66</v>
       </c>
       <c r="B85">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C85">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -1257,10 +1257,10 @@
         <v>67</v>
       </c>
       <c r="B86">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C86">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1268,10 +1268,10 @@
         <v>68</v>
       </c>
       <c r="B87">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C87">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -1279,10 +1279,10 @@
         <v>69</v>
       </c>
       <c r="B88">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C88">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,10 +1290,10 @@
         <v>70</v>
       </c>
       <c r="B89">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C89">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="C90">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="C91">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="C92">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="C93">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="C94">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="C95">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>75</v>
       </c>
       <c r="B96">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C96">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -1378,10 +1378,10 @@
         <v>76</v>
       </c>
       <c r="B97">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C97">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -1389,10 +1389,10 @@
         <v>77</v>
       </c>
       <c r="B98">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C98">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -1400,10 +1400,10 @@
         <v>78</v>
       </c>
       <c r="B99">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C99">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -1411,10 +1411,10 @@
         <v>79</v>
       </c>
       <c r="B100">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C100">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,10 +1422,10 @@
         <v>80</v>
       </c>
       <c r="B101">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C101">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="C102">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -1447,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="C103">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="C104">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="C105">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="C106">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -1491,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="C107">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -1499,10 +1499,10 @@
         <v>85</v>
       </c>
       <c r="B108">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C108">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -1510,10 +1510,10 @@
         <v>86</v>
       </c>
       <c r="B109">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C109">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -1521,10 +1521,10 @@
         <v>87</v>
       </c>
       <c r="B110">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C110">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -1532,10 +1532,10 @@
         <v>88</v>
       </c>
       <c r="B111">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C111">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -1543,10 +1543,10 @@
         <v>89</v>
       </c>
       <c r="B112">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C112">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -1554,10 +1554,10 @@
         <v>90</v>
       </c>
       <c r="B113">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C113">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="C114">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="C115">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="C116">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="C117">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="C118">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="C119">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -1631,10 +1631,10 @@
         <v>95</v>
       </c>
       <c r="B120">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C120">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -1642,10 +1642,10 @@
         <v>96</v>
       </c>
       <c r="B121">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C121">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -1653,10 +1653,10 @@
         <v>97</v>
       </c>
       <c r="B122">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C122">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -1664,10 +1664,10 @@
         <v>98</v>
       </c>
       <c r="B123">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C123">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -1675,10 +1675,10 @@
         <v>99</v>
       </c>
       <c r="B124">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C124">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -1686,10 +1686,10 @@
         <v>100</v>
       </c>
       <c r="B125">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="C125">
-        <v>-66</v>
+        <v>-15</v>
       </c>
     </row>
   </sheetData>
